--- a/documents/excels/11_Tool_Usage_Guideline.xlsx
+++ b/documents/excels/11_Tool_Usage_Guideline.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Xuat bao cao .xlsx gui team review (Summary + Detail + sheet mo ta M001... — dot 9: click ten method o cot B sheet Detail de xem source VB va ASP Core day du body ngay trong Excel). Sheet Detail co 3 cot status: Status (may cham C1-C5) -&gt; 'Status AI danh gia' (AI goi y — dot 6) -&gt; 'Status DEV danh gia' (dropdown de nguoi review chon PASS/WARNING/FAIL/MISSING/EXTRA lam ket luan cuoi — dot 7).</t>
+          <t>Xuat bao cao .xlsx gui team review (Summary + Detail + sheet mo ta M001... — dot 9: click ten method o cot B sheet Detail de xem source VB va ASP Core day du body ngay trong Excel). Sheet Detail co 3 cot status: Status (may cham C1-C5) -&gt; 'Status AI danh gia' (AI goi y — dot 6) -&gt; 'Status DEV danh gia' (dropdown de nguoi review chon PASS/WARNING/FAIL/MISSING/EXTRA lam ket luan cuoi — dot 7). Dong AI cham WARNING co them cot 'AI de xuat giai phap' (tom tat huong sua — dot 12); giai thich chi tiet + code de xuat highlight vang nam trong sheet mo ta Mxxx cua dong do.</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Doc cot 'Noi dung AI danh gia' ben canh; bat AI: config.json muc llm (enabled + api_key — key AIza... lay free tai aistudio.google.com, key sk-ant... tai platform.claude.com).</t>
+          <t>Doc cot 'Noi dung AI danh gia' ben canh; dong WARNING doc them cot 'AI de xuat giai phap' (tom tat huong sua — dot 12) va sheet mo ta Mxxx (giai thich chi tiet + code de xuat, dong sua danh dau '// FIX:'). Bat AI: config.json muc llm (enabled + api_key — key AIza... lay free tai aistudio.google.com, key sk-ant... tai platform.claude.com).</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bat gate danh gia AI qua Claude API (dot 6) — them 2 cot 'Noi dung AI danh gia' / 'Status AI danh gia' vao Excel; can pip install anthropic + API key trong config.json (muc llm) hoac bien moi truong ANTHROPIC_API_KEY; khong anh huong diem C1-C5 va exit code.</t>
+          <t>Bat gate danh gia AI qua Claude API (dot 6) — them cac cot 'Noi dung AI danh gia' / 'Status AI danh gia' / 'AI de xuat giai phap' (dot 12) vao Excel; dong AI cham WARNING co giai thich + code de xuat trong sheet mo ta Mxxx; can pip install anthropic + API key trong config.json (muc llm) hoac bien moi truong ANTHROPIC_API_KEY; khong anh huong diem C1-C5 va exit code.</t>
         </is>
       </c>
     </row>
